--- a/data/chi-square-tests--customer_channel.xlsx
+++ b/data/chi-square-tests--customer_channel.xlsx
@@ -20415,7 +20415,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>WHAT IS CAPTURED: each customer's region and preferred support channel.</t>
+          <t>WHAT IS CAPTURED: each customer's region and preferred support channel (a realistic teaching dataset written for the book).</t>
         </is>
       </c>
     </row>
